--- a/MU/Test upload format/Normal/2027 - 2028/Q2 27-28.xlsx
+++ b/MU/Test upload format/Normal/2027 - 2028/Q2 27-28.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
     <t>SBIN0001235</t>
   </si>
   <si>
-    <t>2728Q2CR701</t>
+    <t>2728Q2CR901</t>
   </si>
   <si>
     <t>900000</t>
@@ -215,7 +215,7 @@
     <t>SBIN0001234</t>
   </si>
   <si>
-    <t>2728Q2CR702</t>
+    <t>2728Q2CR902</t>
   </si>
   <si>
     <t>800000</t>
@@ -233,7 +233,7 @@
     <t>CR703</t>
   </si>
   <si>
-    <t>2728Q2CR703</t>
+    <t>2728Q2CR903</t>
   </si>
   <si>
     <t>500000</t>
@@ -251,7 +251,7 @@
     <t>CR704</t>
   </si>
   <si>
-    <t>2728Q2CR704</t>
+    <t>2728Q2CR904</t>
   </si>
   <si>
     <t>100000</t>
@@ -260,67 +260,67 @@
     <t>CR705</t>
   </si>
   <si>
-    <t>2728Q2CR705</t>
+    <t>2728Q2CR905</t>
   </si>
   <si>
     <t>CR706</t>
   </si>
   <si>
-    <t>2728Q2CR706</t>
+    <t>2728Q2CR906</t>
   </si>
   <si>
     <t>CR707</t>
   </si>
   <si>
-    <t>2728Q2CR707</t>
+    <t>2728Q2CR907</t>
   </si>
   <si>
     <t>CR708</t>
   </si>
   <si>
-    <t>2728Q2CR708</t>
+    <t>2728Q2CR908</t>
   </si>
   <si>
     <t>CR709</t>
   </si>
   <si>
-    <t>2728Q2CR709</t>
+    <t>2728Q2CR909</t>
   </si>
   <si>
     <t>CR710</t>
   </si>
   <si>
-    <t>2728Q2CR710</t>
+    <t>2728Q2CR910</t>
   </si>
   <si>
     <t>CR711</t>
   </si>
   <si>
-    <t>2728Q2CR711</t>
+    <t>2728Q2CR911</t>
   </si>
   <si>
     <t>CR712</t>
   </si>
   <si>
-    <t>2728Q2CR712</t>
+    <t>2728Q2CR912</t>
   </si>
   <si>
     <t>CR713</t>
   </si>
   <si>
-    <t>2728Q2CR713</t>
+    <t>2728Q2CR913</t>
   </si>
   <si>
     <t>CR714</t>
   </si>
   <si>
-    <t>2728Q2CR714</t>
+    <t>2728Q2CR914</t>
   </si>
   <si>
     <t>CR715</t>
   </si>
   <si>
-    <t>2728Q2CR715</t>
+    <t>2728Q2CR915</t>
   </si>
   <si>
     <t>3</t>
@@ -329,7 +329,7 @@
     <t>CR716</t>
   </si>
   <si>
-    <t>2728Q2CR716</t>
+    <t>2728Q2CR916</t>
   </si>
   <si>
     <t>4</t>
@@ -338,7 +338,7 @@
     <t>CR717</t>
   </si>
   <si>
-    <t>2728Q2CR717</t>
+    <t>2728Q2CR917</t>
   </si>
   <si>
     <t>TP</t>
@@ -347,7 +347,7 @@
     <t>CR718</t>
   </si>
   <si>
-    <t>2728Q2CR718</t>
+    <t>2728Q2CR918</t>
   </si>
   <si>
     <t>1000000</t>
@@ -359,37 +359,37 @@
     <t>CR719</t>
   </si>
   <si>
-    <t>2728Q2CR719</t>
+    <t>2728Q2CR919</t>
   </si>
   <si>
     <t>CR720</t>
   </si>
   <si>
-    <t>2728Q2CR720</t>
+    <t>2728Q2CR920</t>
   </si>
   <si>
     <t>CR721</t>
   </si>
   <si>
-    <t>2728Q2CR721</t>
+    <t>2728Q2CR921</t>
   </si>
   <si>
     <t>CR722</t>
   </si>
   <si>
-    <t>2728Q2CR722</t>
+    <t>2728Q2CR922</t>
   </si>
   <si>
     <t>CR723</t>
   </si>
   <si>
-    <t>2728Q2CR723</t>
+    <t>2728Q2CR923</t>
   </si>
   <si>
     <t>CR724</t>
   </si>
   <si>
-    <t>2728Q2CR724</t>
+    <t>2728Q2CR924</t>
   </si>
 </sst>
 </file>
